--- a/Kv11.1_HEK293t_Equine_Human_Pharmacology_long format.xlsx
+++ b/Kv11.1_HEK293t_Equine_Human_Pharmacology_long format.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ugentbe.sharepoint.com/sites/RDM202406315/Work package docs/02_WP2_Patch clamp heterologous cells/Kv11.1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="279" documentId="8_{B5089E7B-B255-4C1F-9EE7-B69743122B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{421B4D47-3813-46C3-A7C9-B2375529B6F8}"/>
+  <xr:revisionPtr revIDLastSave="283" documentId="8_{B5089E7B-B255-4C1F-9EE7-B69743122B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5816AF1-2522-4EFC-9527-1A6ADD3B3DF7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{01C0D836-94F9-4A92-9B80-D0A2425DD813}"/>
   </bookViews>
   <sheets>
-    <sheet name="Flecainide" sheetId="1" r:id="rId1"/>
+    <sheet name="Flecainide - SS activation " sheetId="1" r:id="rId1"/>
+    <sheet name="Flecainide - triple pulse" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -8541,13 +8542,16 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF98AFCF-7077-433C-8585-64B52F03C41D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -8556,7 +8560,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006329CF369658524688C6FC1A94956F40" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4a6dae0628501747292b1398be1665b4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ed29c613-8fed-480e-9c9c-6c000dca3f70" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fd6c29970d69df322389a98b7e2dced2" ns2:_="">
     <xsd:import namespace="ed29c613-8fed-480e-9c9c-6c000dca3f70"/>
@@ -8700,16 +8704,13 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CA74605-89D0-41E9-BAB3-73E0A0C121B1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB0F396C-BCD2-4A4B-BF70-9E5962D86CF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -8717,7 +8718,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F58C292C-2F02-4462-9492-0FAF74F01A99}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8733,4 +8734,13 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CA74605-89D0-41E9-BAB3-73E0A0C121B1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Kv11.1_HEK293t_Equine_Human_Pharmacology_long format.xlsx
+++ b/Kv11.1_HEK293t_Equine_Human_Pharmacology_long format.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ugentbe.sharepoint.com/sites/RDM202406315/Work package docs/02_WP2_Patch clamp heterologous cells/Kv11.1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ugentbe.sharepoint.com/sites/RDM202406315/Work package docs/03_Patch_clamp_HES/Kv11.1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="283" documentId="8_{B5089E7B-B255-4C1F-9EE7-B69743122B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5816AF1-2522-4EFC-9527-1A6ADD3B3DF7}"/>
+  <xr:revisionPtr revIDLastSave="339" documentId="8_{B5089E7B-B255-4C1F-9EE7-B69743122B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E30EDF0B-C692-410E-85CD-EE6A39E0321B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{01C0D836-94F9-4A92-9B80-D0A2425DD813}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{01C0D836-94F9-4A92-9B80-D0A2425DD813}"/>
   </bookViews>
   <sheets>
     <sheet name="Flecainide - SS activation " sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="54">
   <si>
     <t>Species</t>
   </si>
@@ -147,7 +147,58 @@
     <t>Compound_conc_µM</t>
   </si>
   <si>
-    <t>DMSO_conc_%</t>
+    <t>260416_H</t>
+  </si>
+  <si>
+    <t>260416_H_DMSO_0000.abf</t>
+  </si>
+  <si>
+    <t>260416_H_FLEC_0_1_0001.abf</t>
+  </si>
+  <si>
+    <t>260416_H_FLEC_0_3_0000.abf</t>
+  </si>
+  <si>
+    <t>260416_H_FLEC_1_0000.abf</t>
+  </si>
+  <si>
+    <t>260416_H_FLEC_3_0000.abf</t>
+  </si>
+  <si>
+    <t>260416_H_FLEC_10_0000.abf</t>
+  </si>
+  <si>
+    <t>260416_H_FLEC_30_0000.abf</t>
+  </si>
+  <si>
+    <t>260416_H_FLEC_100_0000.abf</t>
+  </si>
+  <si>
+    <t>260416_G_DMSO_0000.abf</t>
+  </si>
+  <si>
+    <t>260416_G_FLEC_0_3_0000.abf</t>
+  </si>
+  <si>
+    <t>260416_G_FLEC_1_0000.abf</t>
+  </si>
+  <si>
+    <t>260416_G_FLEC_3_0000.abf</t>
+  </si>
+  <si>
+    <t>260416_G_FLEC_10_0000.abf</t>
+  </si>
+  <si>
+    <t>260416_G_FLEC_30_0000.abf</t>
+  </si>
+  <si>
+    <t>260416_G_FLEC_100_0000.abf</t>
+  </si>
+  <si>
+    <t>240416_G</t>
+  </si>
+  <si>
+    <t>DMSO_conc</t>
   </si>
 </sst>
 </file>
@@ -541,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6229A30-ABAD-4B7D-B459-51F4B8933871}">
-  <dimension ref="A1:N181"/>
+  <dimension ref="A1:N196"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.5703125" customWidth="1"/>
@@ -565,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>12</v>
@@ -8521,8 +8572,668 @@
         <v>79.265625</v>
       </c>
     </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>13</v>
+      </c>
+      <c r="B182" t="s">
+        <v>36</v>
+      </c>
+      <c r="C182">
+        <v>0.1</v>
+      </c>
+      <c r="D182" t="s">
+        <v>15</v>
+      </c>
+      <c r="E182">
+        <v>0</v>
+      </c>
+      <c r="F182" t="s">
+        <v>37</v>
+      </c>
+      <c r="G182">
+        <v>8.18</v>
+      </c>
+      <c r="H182">
+        <v>3.5</v>
+      </c>
+      <c r="I182">
+        <v>22.9</v>
+      </c>
+      <c r="J182">
+        <v>184.2</v>
+      </c>
+      <c r="K182">
+        <v>-20.2</v>
+      </c>
+      <c r="L182">
+        <v>2000</v>
+      </c>
+      <c r="M182">
+        <v>40</v>
+      </c>
+      <c r="N182">
+        <v>195.940673828125</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>13</v>
+      </c>
+      <c r="B183" t="s">
+        <v>36</v>
+      </c>
+      <c r="C183">
+        <v>0.1</v>
+      </c>
+      <c r="D183" t="s">
+        <v>18</v>
+      </c>
+      <c r="E183">
+        <v>0.1</v>
+      </c>
+      <c r="F183" t="s">
+        <v>38</v>
+      </c>
+      <c r="G183">
+        <v>8.18</v>
+      </c>
+      <c r="H183">
+        <v>3.5</v>
+      </c>
+      <c r="I183">
+        <v>22.9</v>
+      </c>
+      <c r="J183">
+        <v>184.2</v>
+      </c>
+      <c r="K183">
+        <v>-20.2</v>
+      </c>
+      <c r="L183">
+        <v>2000</v>
+      </c>
+      <c r="M183">
+        <v>40</v>
+      </c>
+      <c r="N183">
+        <v>181.59208679199199</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>13</v>
+      </c>
+      <c r="B184" t="s">
+        <v>36</v>
+      </c>
+      <c r="C184">
+        <v>0.1</v>
+      </c>
+      <c r="D184" t="s">
+        <v>18</v>
+      </c>
+      <c r="E184">
+        <v>0.3</v>
+      </c>
+      <c r="F184" t="s">
+        <v>39</v>
+      </c>
+      <c r="G184">
+        <v>8.18</v>
+      </c>
+      <c r="H184">
+        <v>3.5</v>
+      </c>
+      <c r="I184">
+        <v>22.9</v>
+      </c>
+      <c r="J184">
+        <v>184.2</v>
+      </c>
+      <c r="K184">
+        <v>-20.2</v>
+      </c>
+      <c r="L184">
+        <v>2000</v>
+      </c>
+      <c r="M184">
+        <v>40</v>
+      </c>
+      <c r="N184">
+        <v>144.53764343261699</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>13</v>
+      </c>
+      <c r="B185" t="s">
+        <v>36</v>
+      </c>
+      <c r="C185">
+        <v>0.1</v>
+      </c>
+      <c r="D185" t="s">
+        <v>18</v>
+      </c>
+      <c r="E185">
+        <v>1</v>
+      </c>
+      <c r="F185" t="s">
+        <v>40</v>
+      </c>
+      <c r="G185">
+        <v>8.18</v>
+      </c>
+      <c r="H185">
+        <v>3.5</v>
+      </c>
+      <c r="I185">
+        <v>22.9</v>
+      </c>
+      <c r="J185">
+        <v>184.2</v>
+      </c>
+      <c r="K185">
+        <v>-20.2</v>
+      </c>
+      <c r="L185">
+        <v>2000</v>
+      </c>
+      <c r="M185">
+        <v>40</v>
+      </c>
+      <c r="N185">
+        <v>104.895133972167</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>13</v>
+      </c>
+      <c r="B186" t="s">
+        <v>36</v>
+      </c>
+      <c r="C186">
+        <v>0.1</v>
+      </c>
+      <c r="D186" t="s">
+        <v>18</v>
+      </c>
+      <c r="E186">
+        <v>3</v>
+      </c>
+      <c r="F186" t="s">
+        <v>41</v>
+      </c>
+      <c r="G186">
+        <v>8.18</v>
+      </c>
+      <c r="H186">
+        <v>3.5</v>
+      </c>
+      <c r="I186">
+        <v>22.9</v>
+      </c>
+      <c r="J186">
+        <v>184.2</v>
+      </c>
+      <c r="K186">
+        <v>-20.2</v>
+      </c>
+      <c r="L186">
+        <v>2000</v>
+      </c>
+      <c r="M186">
+        <v>40</v>
+      </c>
+      <c r="N186">
+        <v>59.168060302734297</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>13</v>
+      </c>
+      <c r="B187" t="s">
+        <v>36</v>
+      </c>
+      <c r="C187">
+        <v>0.1</v>
+      </c>
+      <c r="D187" t="s">
+        <v>18</v>
+      </c>
+      <c r="E187">
+        <v>10</v>
+      </c>
+      <c r="F187" t="s">
+        <v>42</v>
+      </c>
+      <c r="G187">
+        <v>8.18</v>
+      </c>
+      <c r="H187">
+        <v>3.5</v>
+      </c>
+      <c r="I187">
+        <v>22.9</v>
+      </c>
+      <c r="J187">
+        <v>184.2</v>
+      </c>
+      <c r="K187">
+        <v>-20.2</v>
+      </c>
+      <c r="L187">
+        <v>2000</v>
+      </c>
+      <c r="M187">
+        <v>40</v>
+      </c>
+      <c r="N187">
+        <v>22.176488876342699</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>13</v>
+      </c>
+      <c r="B188" t="s">
+        <v>36</v>
+      </c>
+      <c r="C188">
+        <v>0.1</v>
+      </c>
+      <c r="D188" t="s">
+        <v>18</v>
+      </c>
+      <c r="E188">
+        <v>30</v>
+      </c>
+      <c r="F188" t="s">
+        <v>43</v>
+      </c>
+      <c r="G188">
+        <v>8.18</v>
+      </c>
+      <c r="H188">
+        <v>3.5</v>
+      </c>
+      <c r="I188">
+        <v>22.9</v>
+      </c>
+      <c r="J188">
+        <v>184.2</v>
+      </c>
+      <c r="K188">
+        <v>-20.2</v>
+      </c>
+      <c r="L188">
+        <v>2000</v>
+      </c>
+      <c r="M188">
+        <v>40</v>
+      </c>
+      <c r="N188">
+        <v>4.7900180816650302</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>13</v>
+      </c>
+      <c r="B189" t="s">
+        <v>36</v>
+      </c>
+      <c r="C189">
+        <v>0.1</v>
+      </c>
+      <c r="D189" t="s">
+        <v>18</v>
+      </c>
+      <c r="E189">
+        <v>100</v>
+      </c>
+      <c r="F189" t="s">
+        <v>44</v>
+      </c>
+      <c r="G189">
+        <v>8.18</v>
+      </c>
+      <c r="H189">
+        <v>3.5</v>
+      </c>
+      <c r="I189">
+        <v>22.9</v>
+      </c>
+      <c r="J189">
+        <v>184.2</v>
+      </c>
+      <c r="K189">
+        <v>-20.2</v>
+      </c>
+      <c r="L189">
+        <v>2000</v>
+      </c>
+      <c r="M189">
+        <v>40</v>
+      </c>
+      <c r="N189">
+        <v>-2.9675636291503902</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>11</v>
+      </c>
+      <c r="B190" t="s">
+        <v>52</v>
+      </c>
+      <c r="C190">
+        <v>0.1</v>
+      </c>
+      <c r="D190" t="s">
+        <v>15</v>
+      </c>
+      <c r="E190">
+        <v>0</v>
+      </c>
+      <c r="F190" t="s">
+        <v>45</v>
+      </c>
+      <c r="G190">
+        <v>13.87</v>
+      </c>
+      <c r="H190">
+        <v>790.8</v>
+      </c>
+      <c r="I190">
+        <v>3.8</v>
+      </c>
+      <c r="J190">
+        <v>53</v>
+      </c>
+      <c r="K190">
+        <v>-53.4</v>
+      </c>
+      <c r="L190">
+        <v>2000</v>
+      </c>
+      <c r="M190">
+        <v>40</v>
+      </c>
+      <c r="N190">
+        <v>2526.07763671875</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>11</v>
+      </c>
+      <c r="B191" t="s">
+        <v>52</v>
+      </c>
+      <c r="C191">
+        <v>0.1</v>
+      </c>
+      <c r="D191" t="s">
+        <v>18</v>
+      </c>
+      <c r="E191">
+        <v>0.3</v>
+      </c>
+      <c r="F191" t="s">
+        <v>46</v>
+      </c>
+      <c r="G191">
+        <v>13.87</v>
+      </c>
+      <c r="H191">
+        <v>790.8</v>
+      </c>
+      <c r="I191">
+        <v>3.8</v>
+      </c>
+      <c r="J191">
+        <v>53</v>
+      </c>
+      <c r="K191">
+        <v>-53.4</v>
+      </c>
+      <c r="L191">
+        <v>2000</v>
+      </c>
+      <c r="M191">
+        <v>40</v>
+      </c>
+      <c r="N191">
+        <v>2259.42919921875</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>11</v>
+      </c>
+      <c r="B192" t="s">
+        <v>52</v>
+      </c>
+      <c r="C192">
+        <v>0.1</v>
+      </c>
+      <c r="D192" t="s">
+        <v>18</v>
+      </c>
+      <c r="E192">
+        <v>1</v>
+      </c>
+      <c r="F192" t="s">
+        <v>47</v>
+      </c>
+      <c r="G192">
+        <v>13.87</v>
+      </c>
+      <c r="H192">
+        <v>790.8</v>
+      </c>
+      <c r="I192">
+        <v>3.8</v>
+      </c>
+      <c r="J192">
+        <v>53</v>
+      </c>
+      <c r="K192">
+        <v>-53.4</v>
+      </c>
+      <c r="L192">
+        <v>2000</v>
+      </c>
+      <c r="M192">
+        <v>40</v>
+      </c>
+      <c r="N192">
+        <v>1255.88525390625</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>11</v>
+      </c>
+      <c r="B193" t="s">
+        <v>52</v>
+      </c>
+      <c r="C193">
+        <v>0.1</v>
+      </c>
+      <c r="D193" t="s">
+        <v>18</v>
+      </c>
+      <c r="E193">
+        <v>3</v>
+      </c>
+      <c r="F193" t="s">
+        <v>48</v>
+      </c>
+      <c r="G193">
+        <v>13.87</v>
+      </c>
+      <c r="H193">
+        <v>790.8</v>
+      </c>
+      <c r="I193">
+        <v>3.8</v>
+      </c>
+      <c r="J193">
+        <v>53</v>
+      </c>
+      <c r="K193">
+        <v>-53.4</v>
+      </c>
+      <c r="L193">
+        <v>2000</v>
+      </c>
+      <c r="M193">
+        <v>40</v>
+      </c>
+      <c r="N193">
+        <v>576.38299560546795</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>11</v>
+      </c>
+      <c r="B194" t="s">
+        <v>52</v>
+      </c>
+      <c r="C194">
+        <v>0.1</v>
+      </c>
+      <c r="D194" t="s">
+        <v>18</v>
+      </c>
+      <c r="E194">
+        <v>10</v>
+      </c>
+      <c r="F194" t="s">
+        <v>49</v>
+      </c>
+      <c r="G194">
+        <v>13.87</v>
+      </c>
+      <c r="H194">
+        <v>790.8</v>
+      </c>
+      <c r="I194">
+        <v>3.8</v>
+      </c>
+      <c r="J194">
+        <v>53</v>
+      </c>
+      <c r="K194">
+        <v>-53.4</v>
+      </c>
+      <c r="L194">
+        <v>2000</v>
+      </c>
+      <c r="M194">
+        <v>40</v>
+      </c>
+      <c r="N194">
+        <v>210.055252075195</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>11</v>
+      </c>
+      <c r="B195" t="s">
+        <v>52</v>
+      </c>
+      <c r="C195">
+        <v>0.1</v>
+      </c>
+      <c r="D195" t="s">
+        <v>18</v>
+      </c>
+      <c r="E195">
+        <v>30</v>
+      </c>
+      <c r="F195" t="s">
+        <v>50</v>
+      </c>
+      <c r="G195">
+        <v>13.87</v>
+      </c>
+      <c r="H195">
+        <v>790.8</v>
+      </c>
+      <c r="I195">
+        <v>3.8</v>
+      </c>
+      <c r="J195">
+        <v>53</v>
+      </c>
+      <c r="K195">
+        <v>-53.4</v>
+      </c>
+      <c r="L195">
+        <v>2000</v>
+      </c>
+      <c r="M195">
+        <v>40</v>
+      </c>
+      <c r="N195">
+        <v>57.981239318847599</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>11</v>
+      </c>
+      <c r="B196" t="s">
+        <v>52</v>
+      </c>
+      <c r="C196">
+        <v>0.1</v>
+      </c>
+      <c r="D196" t="s">
+        <v>18</v>
+      </c>
+      <c r="E196">
+        <v>100</v>
+      </c>
+      <c r="F196" t="s">
+        <v>51</v>
+      </c>
+      <c r="G196">
+        <v>13.87</v>
+      </c>
+      <c r="H196">
+        <v>790.8</v>
+      </c>
+      <c r="I196">
+        <v>3.8</v>
+      </c>
+      <c r="J196">
+        <v>53</v>
+      </c>
+      <c r="K196">
+        <v>-53.4</v>
+      </c>
+      <c r="L196">
+        <v>2000</v>
+      </c>
+      <c r="M196">
+        <v>40</v>
+      </c>
+      <c r="N196">
+        <v>3.43468046188354</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A181">
+  <conditionalFormatting sqref="A1:A196">
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Human">
       <formula>NOT(ISERROR(SEARCH("Human",A1)))</formula>
     </cfRule>
@@ -8531,7 +9242,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A181" xr:uid="{2927FE15-1981-4C28-A0D2-8F4E8CA21684}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A196" xr:uid="{2927FE15-1981-4C28-A0D2-8F4E8CA21684}">
       <formula1>"Human, Equine"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{B09CB635-B463-4D53-B845-575F4E54FCB1}">
@@ -8552,6 +9263,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -8560,7 +9277,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006329CF369658524688C6FC1A94956F40" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4a6dae0628501747292b1398be1665b4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ed29c613-8fed-480e-9c9c-6c000dca3f70" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fd6c29970d69df322389a98b7e2dced2" ns2:_="">
     <xsd:import namespace="ed29c613-8fed-480e-9c9c-6c000dca3f70"/>
@@ -8704,13 +9421,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CA74605-89D0-41E9-BAB3-73E0A0C121B1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB0F396C-BCD2-4A4B-BF70-9E5962D86CF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -8718,7 +9438,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F58C292C-2F02-4462-9492-0FAF74F01A99}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8734,13 +9454,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CA74605-89D0-41E9-BAB3-73E0A0C121B1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Kv11.1_HEK293t_Equine_Human_Pharmacology_long format.xlsx
+++ b/Kv11.1_HEK293t_Equine_Human_Pharmacology_long format.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ugentbe.sharepoint.com/sites/RDM202406315/Work package docs/03_Patch_clamp_HES/Kv11.1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R_Projects\Kv11.1 analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="339" documentId="8_{B5089E7B-B255-4C1F-9EE7-B69743122B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E30EDF0B-C692-410E-85CD-EE6A39E0321B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834CB9EC-DFE4-47FB-9F17-AF1E14B704B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{01C0D836-94F9-4A92-9B80-D0A2425DD813}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{01C0D836-94F9-4A92-9B80-D0A2425DD813}"/>
   </bookViews>
   <sheets>
     <sheet name="Flecainide - SS activation " sheetId="1" r:id="rId1"/>
@@ -8613,7 +8613,7 @@
         <v>40</v>
       </c>
       <c r="N182">
-        <v>195.940673828125</v>
+        <v>125.6882738</v>
       </c>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.25">
@@ -8657,7 +8657,7 @@
         <v>40</v>
       </c>
       <c r="N183">
-        <v>181.59208679199199</v>
+        <v>95.089086789999996</v>
       </c>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.25">
@@ -8701,7 +8701,7 @@
         <v>40</v>
       </c>
       <c r="N184">
-        <v>144.53764343261699</v>
+        <v>83.044043430000002</v>
       </c>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.25">
@@ -8745,7 +8745,7 @@
         <v>40</v>
       </c>
       <c r="N185">
-        <v>104.895133972167</v>
+        <v>41.172833969999999</v>
       </c>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.25">
@@ -8789,7 +8789,7 @@
         <v>40</v>
       </c>
       <c r="N186">
-        <v>59.168060302734297</v>
+        <v>15.822660300000001</v>
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.25">
@@ -8833,7 +8833,7 @@
         <v>40</v>
       </c>
       <c r="N187">
-        <v>22.176488876342699</v>
+        <v>3.7206888760000001</v>
       </c>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.25">
@@ -8877,7 +8877,7 @@
         <v>40</v>
       </c>
       <c r="N188">
-        <v>4.7900180816650302</v>
+        <v>0.62866808200000002</v>
       </c>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.25">
@@ -8921,7 +8921,7 @@
         <v>40</v>
       </c>
       <c r="N189">
-        <v>-2.9675636291503902</v>
+        <v>-0.52418362900000004</v>
       </c>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.25">
